--- a/data/trans_bre/P1429-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1429-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>326,01%</t>
+          <t>313,65%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,44</t>
+          <t>0,53; 5,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,0</t>
+          <t>0,21; 3,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,73</t>
+          <t>0,16; 3,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,59</t>
+          <t>0,87; 3,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1430,83</t>
+          <t>5,43; 1522,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,07; 1330,39</t>
+          <t>24,68; 1163,89</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>3,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2384,43%</t>
+          <t>2209,07%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,25</t>
+          <t>-0,23; 3,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,03</t>
+          <t>0,3; 2,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,31</t>
+          <t>0,34; 3,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,63</t>
+          <t>1,95; 4,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 1614,2</t>
+          <t>-43,34; 1670,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,38</t>
+          <t>6,95</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>992,58%</t>
+          <t>661,02%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,81</t>
+          <t>0,79; 7,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,77</t>
+          <t>0,41; 4,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 10,06</t>
+          <t>1,44; 10,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 12,97</t>
+          <t>3,63; 12,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 1651,51</t>
+          <t>3,59; 1631,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,01; 4347,34</t>
+          <t>14,26; 3523,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>295,6; 6201,17</t>
+          <t>181,92; 2351,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>125,77%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,72</t>
+          <t>0,68; 3,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,62</t>
+          <t>0,63; 2,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,2</t>
+          <t>0,97; 2,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,38</t>
+          <t>0,51; 2,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,96; 358,61</t>
+          <t>27,03; 367,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>115,05; —</t>
+          <t>119,97; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>174,86; —</t>
+          <t>128,69; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,4; 236,69</t>
+          <t>14,36; 327,46</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1014,7%</t>
+          <t>1238,45%</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,48</t>
+          <t>0,67; 4,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,06</t>
+          <t>3,69; 7,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,55</t>
+          <t>0,8; 3,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,49</t>
+          <t>4,42; 7,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 1184,14</t>
+          <t>-0,04; 1181,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,19 +1090,19 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,61; 1057,5</t>
+          <t>55,32; 1221,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>304,32; 4417,29</t>
+          <t>374,96; 4773,85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,03</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2956,34%</t>
+          <t>2697,76%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,39</t>
+          <t>4,55; 7,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,23</t>
+          <t>5,0; 8,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,22</t>
+          <t>4,3; 7,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 7,56</t>
+          <t>4,55; 7,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>437,38%</t>
+          <t>470,23%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,08</t>
+          <t>2,55; 4,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,54</t>
+          <t>3,14; 4,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,79</t>
+          <t>2,44; 3,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,32</t>
+          <t>3,34; 4,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>193,97; 519,27</t>
+          <t>197,32; 502,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>727,5; 6605,83</t>
+          <t>759,9; 5886,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>455,71; 1818,1</t>
+          <t>437,83; 1740,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>238,08; 744,56</t>
+          <t>288,94; 753,84</t>
         </is>
       </c>
     </row>
